--- a/data/trans_dic/P1435-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P1435-Clase-trans_dic.xlsx
@@ -628,7 +628,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>9,08%</t>
+          <t>8,79%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -648,7 +648,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>9,08%</t>
+          <t>8,79%</t>
         </is>
       </c>
     </row>
@@ -661,42 +661,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>4,69; 10,44</t>
+          <t>4,72; 10,48</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,57; 7,3</t>
+          <t>2,5; 7,32</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,94; 5,94</t>
+          <t>1,7; 5,79</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6,75; 11,87</t>
+          <t>6,46; 11,51</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>4,69; 10,44</t>
+          <t>4,72; 10,48</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,57; 7,3</t>
+          <t>2,5; 7,32</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,94; 5,94</t>
+          <t>1,7; 5,79</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>6,75; 11,87</t>
+          <t>6,46; 11,51</t>
         </is>
       </c>
     </row>
@@ -728,7 +728,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>7,75%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -748,7 +748,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>7,75%</t>
         </is>
       </c>
     </row>
@@ -761,42 +761,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>10,27; 17,18</t>
+          <t>10,04; 17,51</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,99; 7,53</t>
+          <t>3,05; 7,58</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,11; 6,17</t>
+          <t>2,07; 5,98</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5,53; 10,5</t>
+          <t>5,73; 10,62</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>10,27; 17,18</t>
+          <t>10,04; 17,51</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,99; 7,53</t>
+          <t>3,05; 7,58</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,11; 6,17</t>
+          <t>2,07; 5,98</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>5,53; 10,5</t>
+          <t>5,73; 10,62</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -848,7 +848,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>4,68%</t>
         </is>
       </c>
     </row>
@@ -861,42 +861,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>5,52; 14,92</t>
+          <t>5,33; 14,44</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,55; 6,88</t>
+          <t>1,56; 6,51</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,6; 5,82</t>
+          <t>0,62; 5,58</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,83; 8,29</t>
+          <t>2,24; 8,4</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>5,52; 14,92</t>
+          <t>5,33; 14,44</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,55; 6,88</t>
+          <t>1,56; 6,51</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,6; 5,82</t>
+          <t>0,62; 5,58</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,83; 8,29</t>
+          <t>2,24; 8,4</t>
         </is>
       </c>
     </row>
@@ -928,7 +928,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>7,83%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -948,7 +948,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>7,83%</t>
         </is>
       </c>
     </row>
@@ -961,42 +961,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>7,63; 11,94</t>
+          <t>7,63; 11,91</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>3,44; 6,58</t>
+          <t>3,55; 6,62</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,58; 2,08</t>
+          <t>0,48; 1,98</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2,81; 8,11</t>
+          <t>6,21; 9,9</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>7,63; 11,94</t>
+          <t>7,63; 11,91</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,44; 6,58</t>
+          <t>3,55; 6,62</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,58; 2,08</t>
+          <t>0,48; 1,98</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2,81; 8,11</t>
+          <t>6,21; 9,9</t>
         </is>
       </c>
     </row>
@@ -1028,7 +1028,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>12,6%</t>
+          <t>5,1%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1048,7 +1048,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>12,6%</t>
+          <t>5,1%</t>
         </is>
       </c>
     </row>
@@ -1061,49 +1061,49 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>3,26; 6,87</t>
+          <t>3,16; 6,96</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,8; 4,27</t>
+          <t>1,8; 4,34</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,24; 3,38</t>
+          <t>1,26; 3,16</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4,26; 35,85</t>
+          <t>3,89; 6,62</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>3,26; 6,87</t>
+          <t>3,16; 6,96</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,8; 4,27</t>
+          <t>1,8; 4,34</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,24; 3,38</t>
+          <t>1,26; 3,16</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>4,26; 35,85</t>
+          <t>3,89; 6,62</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1128,7 +1128,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1148,7 +1148,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,19%</t>
         </is>
       </c>
     </row>
@@ -1161,42 +1161,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>4,99; 7,51</t>
+          <t>4,88; 7,42</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2,38; 4,68</t>
+          <t>2,43; 4,72</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,55; 1,79</t>
+          <t>0,55; 1,88</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1,76; 5,32</t>
+          <t>1,81; 5,17</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>4,99; 7,51</t>
+          <t>4,88; 7,42</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2,38; 4,68</t>
+          <t>2,43; 4,72</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,55; 1,79</t>
+          <t>0,55; 1,88</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1,76; 5,32</t>
+          <t>1,81; 5,17</t>
         </is>
       </c>
     </row>
@@ -1228,7 +1228,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>7,39%</t>
+          <t>6,08%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>7,39%</t>
+          <t>6,08%</t>
         </is>
       </c>
     </row>
@@ -1261,42 +1261,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>6,93; 8,65</t>
+          <t>6,92; 8,62</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>3,21; 4,59</t>
+          <t>3,25; 4,59</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,47; 2,42</t>
+          <t>1,47; 2,38</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>5,27; 15,58</t>
+          <t>5,29; 6,98</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>6,93; 8,65</t>
+          <t>6,92; 8,62</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>3,21; 4,59</t>
+          <t>3,25; 4,59</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,47; 2,42</t>
+          <t>1,47; 2,38</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>5,27; 15,58</t>
+          <t>5,29; 6,98</t>
         </is>
       </c>
     </row>
@@ -1501,7 +1501,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>40498</t>
+          <t>42805</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1521,7 +1521,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>40498</t>
+          <t>42805</t>
         </is>
       </c>
     </row>
@@ -1534,42 +1534,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>14384; 32019</t>
+          <t>14467; 32140</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>8086; 22959</t>
+          <t>7876; 23023</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>6747; 20602</t>
+          <t>5888; 20101</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>30116; 52926</t>
+          <t>31443; 56044</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>14384; 32019</t>
+          <t>14467; 32140</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>8086; 22959</t>
+          <t>7876; 23023</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>6747; 20602</t>
+          <t>5888; 20101</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>30116; 52926</t>
+          <t>31443; 56044</t>
         </is>
       </c>
     </row>
@@ -1649,7 +1649,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>29322</t>
+          <t>32650</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1669,7 +1669,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>29322</t>
+          <t>32650</t>
         </is>
       </c>
     </row>
@@ -1682,42 +1682,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>38199; 63879</t>
+          <t>37345; 65108</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>10091; 25438</t>
+          <t>10296; 25611</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>7862; 22956</t>
+          <t>7692; 22270</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>21051; 39976</t>
+          <t>24119; 44734</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>38199; 63879</t>
+          <t>37345; 65108</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>10091; 25438</t>
+          <t>10296; 25611</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>7862; 22956</t>
+          <t>7692; 22270</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>21051; 39976</t>
+          <t>24119; 44734</t>
         </is>
       </c>
     </row>
@@ -1797,7 +1797,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>6647</t>
+          <t>8766</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1817,7 +1817,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>6647</t>
+          <t>8766</t>
         </is>
       </c>
     </row>
@@ -1830,42 +1830,42 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>9266; 25028</t>
+          <t>8937; 24229</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>4045; 17904</t>
+          <t>4059; 16924</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1000; 9676</t>
+          <t>1029; 9277</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>3047; 13834</t>
+          <t>4203; 15754</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>9266; 25028</t>
+          <t>8937; 24229</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>4045; 17904</t>
+          <t>4059; 16924</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>1000; 9676</t>
+          <t>1029; 9277</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>3047; 13834</t>
+          <t>4203; 15754</t>
         </is>
       </c>
     </row>
@@ -1945,7 +1945,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>57834</t>
+          <t>67143</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1965,7 +1965,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>57834</t>
+          <t>67143</t>
         </is>
       </c>
     </row>
@@ -1978,42 +1978,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>54519; 85252</t>
+          <t>54524; 85060</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>26278; 50284</t>
+          <t>27147; 50642</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>4755; 17191</t>
+          <t>3925; 16328</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>27440; 79109</t>
+          <t>53238; 84895</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>54519; 85252</t>
+          <t>54524; 85060</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>26278; 50284</t>
+          <t>27147; 50642</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>4755; 17191</t>
+          <t>3925; 16328</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>27440; 79109</t>
+          <t>53238; 84895</t>
         </is>
       </c>
     </row>
@@ -2093,7 +2093,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>105493</t>
+          <t>42222</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2113,7 +2113,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>105493</t>
+          <t>42222</t>
         </is>
       </c>
     </row>
@@ -2126,49 +2126,49 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>18567; 39060</t>
+          <t>17970; 39585</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>13659; 32477</t>
+          <t>13713; 32996</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>9161; 24940</t>
+          <t>9310; 23338</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>35685; 300223</t>
+          <t>32203; 54825</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>18567; 39060</t>
+          <t>17970; 39585</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>13659; 32477</t>
+          <t>13713; 32996</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>9161; 24940</t>
+          <t>9310; 23338</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>35685; 300223</t>
+          <t>32203; 54825</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2241,7 +2241,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>23685</t>
+          <t>26937</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2261,7 +2261,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>23685</t>
+          <t>26937</t>
         </is>
       </c>
     </row>
@@ -2274,42 +2274,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>62330; 93823</t>
+          <t>60992; 92668</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>26381; 51945</t>
+          <t>26990; 52321</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>5914; 19324</t>
+          <t>5919; 20291</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>13391; 40504</t>
+          <t>15296; 43618</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>62330; 93823</t>
+          <t>60992; 92668</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>26381; 51945</t>
+          <t>26990; 52321</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>5914; 19324</t>
+          <t>5919; 20291</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>13391; 40504</t>
+          <t>15296; 43618</t>
         </is>
       </c>
     </row>
@@ -2389,7 +2389,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>263480</t>
+          <t>220523</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2409,7 +2409,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>263480</t>
+          <t>220523</t>
         </is>
       </c>
     </row>
@@ -2422,42 +2422,42 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>234102; 292170</t>
+          <t>233670; 291268</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>113834; 162706</t>
+          <t>115409; 162708</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>51849; 85345</t>
+          <t>51846; 84151</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>188120; 555773</t>
+          <t>191780; 252976</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>234102; 292170</t>
+          <t>233670; 291268</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>113834; 162706</t>
+          <t>115409; 162708</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>51849; 85345</t>
+          <t>51846; 84151</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>188120; 555773</t>
+          <t>191780; 252976</t>
         </is>
       </c>
     </row>
